--- a/Data/EventData/SCE_2022.xlsx
+++ b/Data/EventData/SCE_2022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edisonintl-my.sharepoint.com/personal/peter_dugan_sce_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dread\Downloads\Wildfire-Point-Process\Data\EventData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{972455CB-680D-4C3C-AAF1-61318250DF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7F166F3-DDD2-46CF-8005-92351CAFD717}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC83F4A-AB67-4384-AD08-EB5A12641C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{BD3B2349-B642-438F-89D4-EB7FD184DA6D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD3B2349-B642-438F-89D4-EB7FD184DA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="2022 Reportables" sheetId="2" r:id="rId1"/>
@@ -410,7 +410,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="264">
   <si>
     <t>Contact From Object</t>
   </si>
@@ -888,9 +888,6 @@
   </si>
   <si>
     <t>UG-5516998</t>
-  </si>
-  <si>
-    <t>13;23</t>
   </si>
   <si>
     <t>34.138815</t>
@@ -1211,7 +1208,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
@@ -1506,7 +1503,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1699,6 +1696,42 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1741,46 +1774,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1788,63 +1781,7 @@
     <cellStyle name="Normal 4" xfId="2" xr:uid="{E5E82BBC-A907-4CED-A4DF-30ED5A31C5C1}"/>
     <cellStyle name="Normal_Sheet1" xfId="3" xr:uid="{56BD7D50-FC1C-428A-824D-7229A0485B36}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1874,7 +1811,9 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{18B3B590-E972-4BC7-9AC5-6D1AF69B6D95}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1887,7 +1826,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="CPUC Sample Interactive"/>
@@ -2166,9 +2105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2206,7 +2145,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2312,7 +2251,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2454,7 +2393,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2462,74 +2401,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090D82BB-7471-40DB-BECD-CE894B1F314E}">
-  <dimension ref="A1:X128"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W128"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="33.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" customWidth="1"/>
-    <col min="12" max="12" width="26.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" customWidth="1"/>
+    <col min="10" max="10" width="33.5546875" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" customWidth="1"/>
+    <col min="12" max="12" width="26.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" customWidth="1"/>
+    <col min="23" max="23" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="72" t="s">
+      <c r="C1" s="81"/>
+      <c r="D1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74" t="s">
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="76" t="s">
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="78" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="66" t="s">
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-    </row>
-    <row r="2" spans="1:23" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="71"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+    </row>
+    <row r="2" spans="1:23" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="83"/>
       <c r="B2" s="44" t="s">
         <v>7</v>
       </c>
@@ -2597,7 +2536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2614,35 +2553,35 @@
         <v>-118.150291</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>163</v>
-      </c>
       <c r="H3" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J3" s="45"/>
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M3" s="3">
         <v>16</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P3" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q3" s="54">
         <v>44567</v>
@@ -2655,16 +2594,16 @@
       </c>
       <c r="T3" s="60"/>
       <c r="U3" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V3" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V3" s="61" t="s">
+      <c r="W3" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W3" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -2681,37 +2620,37 @@
         <v>-118.04358499999999</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>163</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J4" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M4" s="3">
         <v>4</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P4" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="55"/>
@@ -2720,16 +2659,16 @@
       </c>
       <c r="T4" s="60"/>
       <c r="U4" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V4" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W4" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W4" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
@@ -2746,37 +2685,37 @@
         <v>-116.527507</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J5" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M5" s="3">
         <v>12</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P5" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q5" s="54">
         <v>44573</v>
@@ -2789,16 +2728,16 @@
       </c>
       <c r="T5" s="60"/>
       <c r="U5" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V5" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V5" s="61" t="s">
+      <c r="W5" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W5" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>1</v>
       </c>
@@ -2809,55 +2748,55 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="F6" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H6" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J6" s="45"/>
       <c r="K6" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M6" s="3">
         <v>16</v>
       </c>
       <c r="N6" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="O6" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="O6" s="30" t="s">
-        <v>232</v>
-      </c>
       <c r="P6" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q6" s="54"/>
       <c r="R6" s="55"/>
       <c r="S6" s="59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T6" s="60"/>
       <c r="U6" s="60"/>
       <c r="V6" s="45"/>
       <c r="W6" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>1</v>
       </c>
@@ -2874,37 +2813,37 @@
         <v>-117.627533</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M7" s="3">
         <v>12</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O7" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="O7" s="30" t="s">
-        <v>232</v>
-      </c>
       <c r="P7" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q7" s="54"/>
       <c r="R7" s="55"/>
@@ -2913,16 +2852,16 @@
       </c>
       <c r="T7" s="60"/>
       <c r="U7" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V7" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W7" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>1</v>
       </c>
@@ -2939,37 +2878,37 @@
         <v>-117.33408</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J8" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M8" s="3">
         <v>12</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="O8" s="30" t="s">
-        <v>232</v>
-      </c>
       <c r="P8" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q8" s="54">
         <v>44584</v>
@@ -2982,16 +2921,16 @@
       </c>
       <c r="T8" s="60"/>
       <c r="U8" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V8" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V8" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W8" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>1</v>
       </c>
@@ -3008,35 +2947,35 @@
         <v>-118.195183</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J9" s="45"/>
       <c r="K9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M9" s="3">
         <v>16</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P9" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q9" s="54">
         <v>44586</v>
@@ -3049,16 +2988,16 @@
       </c>
       <c r="T9" s="60"/>
       <c r="U9" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V9" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W9" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W9" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>1</v>
       </c>
@@ -3075,53 +3014,53 @@
         <v>-118.00175</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M10" s="3">
         <v>16</v>
       </c>
       <c r="N10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P10" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q10" s="54"/>
       <c r="R10" s="55"/>
       <c r="S10" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T10" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U10" s="60"/>
       <c r="V10" s="45"/>
       <c r="W10" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>1</v>
       </c>
@@ -3138,53 +3077,53 @@
         <v>-118.895309</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G11" s="18" t="s">
-        <v>163</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M11" s="3">
         <v>16</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P11" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q11" s="54"/>
       <c r="R11" s="55"/>
       <c r="S11" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T11" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U11" s="60"/>
       <c r="V11" s="45"/>
       <c r="W11" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>1</v>
       </c>
@@ -3201,37 +3140,37 @@
         <v>-118.896585</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M12" s="3">
         <v>16</v>
       </c>
       <c r="N12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P12" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="54">
         <v>44596</v>
@@ -3244,16 +3183,16 @@
       </c>
       <c r="T12" s="60"/>
       <c r="U12" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V12" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W12" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
@@ -3270,37 +3209,37 @@
         <v>-119.213415</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J13" s="46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M13" s="3">
         <v>12</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P13" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q13" s="54">
         <v>44596</v>
@@ -3309,18 +3248,18 @@
         <v>0.65763888888888888</v>
       </c>
       <c r="S13" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T13" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U13" s="60"/>
       <c r="V13" s="45"/>
       <c r="W13" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>1</v>
       </c>
@@ -3337,35 +3276,35 @@
         <v>-119.241694</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J14" s="45"/>
       <c r="K14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M14" s="3">
         <v>12</v>
       </c>
       <c r="N14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O14" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P14" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q14" s="54">
         <v>44599</v>
@@ -3374,18 +3313,18 @@
         <v>0.36180555555555555</v>
       </c>
       <c r="S14" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="T14" s="59" t="s">
         <v>250</v>
-      </c>
-      <c r="T14" s="59" t="s">
-        <v>251</v>
       </c>
       <c r="U14" s="60"/>
       <c r="V14" s="45"/>
       <c r="W14" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>1</v>
       </c>
@@ -3402,35 +3341,35 @@
         <v>-118.80593</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J15" s="45"/>
       <c r="K15" s="3" t="s">
         <v>52</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M15" s="3">
         <v>16</v>
       </c>
       <c r="N15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O15" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P15" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q15" s="54"/>
       <c r="R15" s="55"/>
@@ -3439,16 +3378,16 @@
       </c>
       <c r="T15" s="60"/>
       <c r="U15" s="59" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V15" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W15" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W15" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>1</v>
       </c>
@@ -3465,51 +3404,51 @@
         <v>-118.126482</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J16" s="45"/>
       <c r="K16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M16" s="3">
         <v>16</v>
       </c>
       <c r="N16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O16" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P16" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q16" s="54"/>
       <c r="R16" s="55"/>
       <c r="S16" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T16" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U16" s="60"/>
       <c r="V16" s="45"/>
       <c r="W16" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>1</v>
       </c>
@@ -3526,35 +3465,35 @@
         <v>-116.47417</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J17" s="47"/>
       <c r="K17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M17" s="3">
         <v>33</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P17" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q17" s="54">
         <v>44605</v>
@@ -3563,18 +3502,18 @@
         <v>0.45763888888888887</v>
       </c>
       <c r="S17" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T17" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U17" s="60"/>
       <c r="V17" s="60"/>
       <c r="W17" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>1</v>
       </c>
@@ -3591,37 +3530,37 @@
         <v>-117.45811</v>
       </c>
       <c r="F18" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>163</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M18" s="3">
         <v>12</v>
       </c>
       <c r="N18" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O18" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P18" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q18" s="54">
         <v>44606</v>
@@ -3634,16 +3573,16 @@
       </c>
       <c r="T18" s="60"/>
       <c r="U18" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V18" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V18" s="61" t="s">
+      <c r="W18" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W18" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>1</v>
       </c>
@@ -3660,37 +3599,37 @@
         <v>-119.471873</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J19" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M19" s="3">
         <v>16</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P19" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q19" s="54">
         <v>44607</v>
@@ -3703,16 +3642,16 @@
       </c>
       <c r="T19" s="60"/>
       <c r="U19" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V19" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W19" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>1</v>
       </c>
@@ -3729,35 +3668,35 @@
         <v>-117.593458</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H20" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J20" s="45"/>
       <c r="K20" s="3" t="s">
         <v>57</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M20" s="3">
         <v>12</v>
       </c>
       <c r="N20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P20" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q20" s="54">
         <v>44615</v>
@@ -3770,24 +3709,24 @@
       </c>
       <c r="T20" s="60"/>
       <c r="U20" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V20" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W20" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W20" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="10">
         <v>44621</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>159</v>
+      <c r="C21" s="9">
+        <v>0.55763888888888891</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>28</v>
@@ -3796,35 +3735,35 @@
         <v>29</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H21" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J21" s="45"/>
       <c r="K21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M21" s="3">
         <v>16</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P21" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q21" s="54">
         <v>44621</v>
@@ -3833,18 +3772,18 @@
         <v>0.60277777777777775</v>
       </c>
       <c r="S21" s="59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T21" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U21" s="62"/>
       <c r="V21" s="62"/>
       <c r="W21" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>1</v>
       </c>
@@ -3861,37 +3800,37 @@
         <v>-117.90448000000001</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M22" s="3">
         <v>12</v>
       </c>
       <c r="N22" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P22" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q22" s="54">
         <v>44628</v>
@@ -3904,16 +3843,16 @@
       </c>
       <c r="T22" s="60"/>
       <c r="U22" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="V22" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V22" s="61" t="s">
+      <c r="W22" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W22" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
         <v>1</v>
       </c>
@@ -3930,37 +3869,37 @@
         <v>-118.137197</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J23" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>62</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M23" s="3">
         <v>16</v>
       </c>
       <c r="N23" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O23" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P23" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q23" s="54">
         <v>44631</v>
@@ -3973,16 +3912,16 @@
       </c>
       <c r="T23" s="51"/>
       <c r="U23" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="V23" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V23" s="61" t="s">
+      <c r="W23" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W23" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>1</v>
       </c>
@@ -3999,37 +3938,37 @@
         <v>-117.40458599999999</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>60</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M24" s="3">
         <v>12</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O24" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P24" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q24" s="54"/>
       <c r="R24" s="55"/>
@@ -4038,16 +3977,16 @@
       </c>
       <c r="T24" s="51"/>
       <c r="U24" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="V24" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V24" s="61" t="s">
+      <c r="W24" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W24" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>1</v>
       </c>
@@ -4064,37 +4003,37 @@
         <v>-116.94986</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M25" s="3">
         <v>12</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O25" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P25" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q25" s="54">
         <v>44631</v>
@@ -4107,16 +4046,16 @@
       </c>
       <c r="T25" s="51"/>
       <c r="U25" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V25" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W25" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W25" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>1</v>
       </c>
@@ -4133,37 +4072,37 @@
         <v>31</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M26" s="3">
         <v>12</v>
       </c>
       <c r="N26" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P26" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q26" s="54"/>
       <c r="R26" s="55"/>
@@ -4172,16 +4111,16 @@
       </c>
       <c r="T26" s="51"/>
       <c r="U26" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="V26" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V26" s="61" t="s">
+      <c r="W26" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W26" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>1</v>
       </c>
@@ -4198,37 +4137,37 @@
         <v>33</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H27" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J27" s="46" t="s">
         <v>168</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J27" s="46" t="s">
-        <v>169</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>64</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M27" s="3">
         <v>12</v>
       </c>
       <c r="N27" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O27" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P27" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q27" s="54">
         <v>44643</v>
@@ -4241,16 +4180,16 @@
       </c>
       <c r="T27" s="51"/>
       <c r="U27" s="63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V27" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W27" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W27" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>1</v>
       </c>
@@ -4267,35 +4206,35 @@
         <v>-119.900412</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H28" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J28" s="45"/>
       <c r="K28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M28" s="3">
         <v>16</v>
       </c>
       <c r="N28" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P28" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q28" s="54">
         <v>44647</v>
@@ -4304,16 +4243,16 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="S28" s="59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T28" s="51"/>
       <c r="U28" s="51"/>
       <c r="V28" s="45"/>
       <c r="W28" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>1</v>
       </c>
@@ -4330,35 +4269,35 @@
         <v>-117.62118</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J29" s="45"/>
       <c r="K29" s="3" t="s">
         <v>66</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M29" s="3">
         <v>33</v>
       </c>
       <c r="N29" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O29" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P29" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q29" s="54">
         <v>44648</v>
@@ -4367,18 +4306,18 @@
         <v>0.68888888888888899</v>
       </c>
       <c r="S29" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T29" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U29" s="60"/>
       <c r="V29" s="60"/>
       <c r="W29" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>1</v>
       </c>
@@ -4395,35 +4334,35 @@
         <v>-117.74542099999999</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H30" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J30" s="47"/>
       <c r="K30" s="3" t="s">
         <v>67</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M30" s="3">
         <v>12</v>
       </c>
       <c r="N30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O30" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P30" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q30" s="54">
         <v>44653</v>
@@ -4436,16 +4375,16 @@
       </c>
       <c r="T30" s="60"/>
       <c r="U30" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V30" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="V30" s="59" t="s">
-        <v>249</v>
-      </c>
       <c r="W30" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>1</v>
       </c>
@@ -4462,35 +4401,35 @@
         <v>-118.913927</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H31" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J31" s="47"/>
       <c r="K31" s="3" t="s">
         <v>68</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M31" s="3">
         <v>16</v>
       </c>
       <c r="N31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P31" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q31" s="54"/>
       <c r="R31" s="55"/>
@@ -4499,16 +4438,16 @@
       </c>
       <c r="T31" s="60"/>
       <c r="U31" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V31" s="59" t="s">
         <v>242</v>
       </c>
-      <c r="V31" s="59" t="s">
+      <c r="W31" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W31" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>1</v>
       </c>
@@ -4525,37 +4464,37 @@
         <v>-117.917922</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G32" s="18" t="s">
-        <v>163</v>
-      </c>
       <c r="H32" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J32" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M32" s="3">
         <v>12</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P32" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q32" s="54">
         <v>44659</v>
@@ -4568,16 +4507,16 @@
       </c>
       <c r="T32" s="60"/>
       <c r="U32" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V32" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W32" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W32" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>1</v>
       </c>
@@ -4594,37 +4533,37 @@
         <v>-119.92336299999999</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J33" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M33" s="3">
         <v>16</v>
       </c>
       <c r="N33" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P33" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q33" s="54">
         <v>44664</v>
@@ -4637,16 +4576,16 @@
       </c>
       <c r="T33" s="51"/>
       <c r="U33" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V33" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="V33" s="59" t="s">
-        <v>249</v>
-      </c>
       <c r="W33" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>1</v>
       </c>
@@ -4663,35 +4602,35 @@
         <v>-119.92265999999999</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" s="47"/>
       <c r="K34" s="3" t="s">
         <v>71</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M34" s="3">
         <v>16</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P34" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q34" s="54">
         <v>44664</v>
@@ -4700,18 +4639,18 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="S34" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T34" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U34" s="60"/>
       <c r="V34" s="60"/>
       <c r="W34" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
         <v>1</v>
       </c>
@@ -4728,37 +4667,37 @@
         <v>-118.970568</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J35" s="48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M35" s="3">
         <v>66</v>
       </c>
       <c r="N35" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P35" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q35" s="54"/>
       <c r="R35" s="55"/>
@@ -4767,16 +4706,16 @@
       </c>
       <c r="T35" s="60"/>
       <c r="U35" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V35" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W35" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W35" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>1</v>
       </c>
@@ -4793,37 +4732,37 @@
         <v>-118.203188</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J36" s="48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>72</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M36" s="3">
         <v>12</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O36" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O36" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P36" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q36" s="54">
         <v>44667</v>
@@ -4836,16 +4775,16 @@
       </c>
       <c r="T36" s="60"/>
       <c r="U36" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V36" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V36" s="61" t="s">
+      <c r="W36" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W36" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>1</v>
       </c>
@@ -4862,35 +4801,35 @@
         <v>-116.60750400000001</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J37" s="47"/>
       <c r="K37" s="3" t="s">
         <v>73</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M37" s="3">
         <v>33</v>
       </c>
       <c r="N37" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O37" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O37" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P37" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q37" s="54">
         <v>44673</v>
@@ -4899,18 +4838,18 @@
         <v>0.29444444444444445</v>
       </c>
       <c r="S37" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T37" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U37" s="60"/>
       <c r="V37" s="61"/>
       <c r="W37" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>1</v>
       </c>
@@ -4927,37 +4866,37 @@
         <v>-117.817442</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J38" s="48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M38" s="3">
         <v>12</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P38" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q38" s="54">
         <v>44674</v>
@@ -4966,18 +4905,18 @@
         <v>0.41111111111111115</v>
       </c>
       <c r="S38" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T38" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U38" s="60"/>
       <c r="V38" s="61"/>
       <c r="W38" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>1</v>
       </c>
@@ -4994,35 +4933,35 @@
         <v>-118.01986599999999</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H39" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J39" s="47"/>
       <c r="K39" s="3" t="s">
         <v>75</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M39" s="3">
         <v>12</v>
       </c>
       <c r="N39" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O39" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O39" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P39" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q39" s="54">
         <v>44675</v>
@@ -5035,16 +4974,16 @@
       </c>
       <c r="T39" s="60"/>
       <c r="U39" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V39" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V39" s="61" t="s">
+      <c r="W39" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W39" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>1</v>
       </c>
@@ -5061,35 +5000,35 @@
         <v>-117.551215</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J40" s="47"/>
       <c r="K40" s="3" t="s">
         <v>76</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M40" s="3">
         <v>12</v>
       </c>
       <c r="N40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O40" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O40" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P40" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q40" s="54">
         <v>44686</v>
@@ -5098,18 +5037,18 @@
         <v>0.4381944444444445</v>
       </c>
       <c r="S40" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T40" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U40" s="60"/>
       <c r="V40" s="61"/>
       <c r="W40" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>1</v>
       </c>
@@ -5126,35 +5065,35 @@
         <v>-116.546307</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I41" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J41" s="47"/>
       <c r="K41" s="3" t="s">
         <v>77</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M41" s="3">
         <v>33</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P41" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q41" s="54">
         <v>44687</v>
@@ -5163,18 +5102,18 @@
         <v>0.76527777777777783</v>
       </c>
       <c r="S41" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T41" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U41" s="60"/>
       <c r="V41" s="61"/>
       <c r="W41" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>1</v>
       </c>
@@ -5191,37 +5130,37 @@
         <v>-117.281004</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J42" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>79</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M42" s="3">
         <v>12</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P42" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q42" s="54"/>
       <c r="R42" s="55"/>
@@ -5230,16 +5169,16 @@
       </c>
       <c r="T42" s="60"/>
       <c r="U42" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V42" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W42" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W42" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
         <v>1</v>
       </c>
@@ -5256,37 +5195,37 @@
         <v>-119.74069900000001</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J43" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>78</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M43" s="3">
         <v>4.16</v>
       </c>
       <c r="N43" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O43" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O43" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P43" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q43" s="54"/>
       <c r="R43" s="55"/>
@@ -5295,16 +5234,16 @@
       </c>
       <c r="T43" s="60"/>
       <c r="U43" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V43" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W43" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W43" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>1</v>
       </c>
@@ -5321,37 +5260,37 @@
         <v>-118.171401</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J44" s="48" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>80</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M44" s="3">
         <v>16</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P44" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q44" s="54">
         <v>44689</v>
@@ -5364,16 +5303,16 @@
       </c>
       <c r="T44" s="60"/>
       <c r="U44" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V44" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W44" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W44" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
         <v>1</v>
       </c>
@@ -5390,37 +5329,37 @@
         <v>-119.21736300000001</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J45" s="48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>81</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M45" s="3">
         <v>12</v>
       </c>
       <c r="N45" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O45" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P45" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q45" s="54">
         <v>44692</v>
@@ -5433,16 +5372,16 @@
       </c>
       <c r="T45" s="60"/>
       <c r="U45" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V45" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W45" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W45" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>1</v>
       </c>
@@ -5459,51 +5398,51 @@
         <v>-117.962558</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H46" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J46" s="47"/>
       <c r="K46" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M46" s="3">
         <v>12</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P46" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q46" s="54"/>
       <c r="R46" s="55"/>
       <c r="S46" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T46" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U46" s="60"/>
       <c r="V46" s="61"/>
       <c r="W46" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
         <v>1</v>
       </c>
@@ -5520,35 +5459,35 @@
         <v>34</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H47" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J47" s="47"/>
       <c r="K47" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M47" s="3">
         <v>33</v>
       </c>
       <c r="N47" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O47" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O47" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P47" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q47" s="54">
         <v>44695</v>
@@ -5557,18 +5496,18 @@
         <v>0.48888888888888887</v>
       </c>
       <c r="S47" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T47" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U47" s="60"/>
       <c r="V47" s="61"/>
       <c r="W47" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
         <v>1</v>
       </c>
@@ -5585,37 +5524,37 @@
         <v>-117.24562</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J48" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M48" s="3">
         <v>4.16</v>
       </c>
       <c r="N48" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O48" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O48" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P48" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q48" s="54">
         <v>44695</v>
@@ -5624,18 +5563,18 @@
         <v>0.73402777777777783</v>
       </c>
       <c r="S48" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T48" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U48" s="60"/>
       <c r="V48" s="61"/>
       <c r="W48" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
         <v>1</v>
       </c>
@@ -5652,35 +5591,35 @@
         <v>-118.125827</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H49" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J49" s="49"/>
       <c r="K49" s="3" t="s">
         <v>84</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M49" s="3">
         <v>12</v>
       </c>
       <c r="N49" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O49" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O49" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P49" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q49" s="54">
         <v>44697</v>
@@ -5689,18 +5628,18 @@
         <v>0.9458333333333333</v>
       </c>
       <c r="S49" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T49" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U49" s="60"/>
       <c r="V49" s="61"/>
       <c r="W49" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>1</v>
       </c>
@@ -5717,37 +5656,37 @@
         <v>-117.204982</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J50" s="48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>85</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M50" s="3">
         <v>12</v>
       </c>
       <c r="N50" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O50" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O50" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P50" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q50" s="54"/>
       <c r="R50" s="55"/>
@@ -5756,16 +5695,16 @@
       </c>
       <c r="T50" s="60"/>
       <c r="U50" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V50" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W50" s="61" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>1</v>
       </c>
@@ -5782,37 +5721,37 @@
         <v>-116.58602999999999</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J51" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M51" s="3">
         <v>33</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P51" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q51" s="54">
         <v>44699</v>
@@ -5821,18 +5760,18 @@
         <v>0.64374999999999993</v>
       </c>
       <c r="S51" s="59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T51" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U51" s="60"/>
       <c r="V51" s="61"/>
       <c r="W51" s="61" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>1</v>
       </c>
@@ -5849,37 +5788,37 @@
         <v>-117.82659</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J52" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>87</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M52" s="3">
         <v>12</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P52" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q52" s="54"/>
       <c r="R52" s="55"/>
@@ -5887,19 +5826,19 @@
         <v>0</v>
       </c>
       <c r="T52" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U52" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V52" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W52" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W52" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
         <v>1</v>
       </c>
@@ -5916,35 +5855,35 @@
         <v>-118.012539</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J53" s="49"/>
       <c r="K53" s="3" t="s">
         <v>88</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M53" s="3">
         <v>12</v>
       </c>
       <c r="N53" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O53" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O53" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P53" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q53" s="54">
         <v>44704</v>
@@ -5957,16 +5896,16 @@
       </c>
       <c r="T53" s="60"/>
       <c r="U53" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V53" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V53" s="61" t="s">
+      <c r="W53" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W53" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>1</v>
       </c>
@@ -5983,51 +5922,51 @@
         <v>-119.11830500000001</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J54" s="48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>89</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M54" s="3">
         <v>66</v>
       </c>
       <c r="N54" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O54" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O54" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P54" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q54" s="54"/>
       <c r="R54" s="55"/>
       <c r="S54" s="59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T54" s="60"/>
       <c r="U54" s="60"/>
       <c r="V54" s="61"/>
       <c r="W54" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>1</v>
       </c>
@@ -6044,35 +5983,35 @@
         <v>-116.146151</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H55" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I55" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J55" s="49"/>
       <c r="K55" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M55" s="3">
         <v>25</v>
       </c>
       <c r="N55" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O55" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O55" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P55" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q55" s="54">
         <v>44709</v>
@@ -6081,18 +6020,18 @@
         <v>5.347222222222222E-2</v>
       </c>
       <c r="S55" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T55" s="59" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U55" s="60"/>
       <c r="V55" s="61"/>
       <c r="W55" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>1</v>
       </c>
@@ -6109,53 +6048,53 @@
         <v>-118.82067499999999</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J56" s="48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>92</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M56" s="3">
         <v>66</v>
       </c>
       <c r="N56" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O56" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O56" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P56" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q56" s="54"/>
       <c r="R56" s="55"/>
       <c r="S56" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T56" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U56" s="60"/>
       <c r="V56" s="61"/>
       <c r="W56" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>1</v>
       </c>
@@ -6172,35 +6111,35 @@
         <v>-118.189722</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H57" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J57" s="49"/>
       <c r="K57" s="3" t="s">
         <v>90</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M57" s="3">
         <v>12</v>
       </c>
       <c r="N57" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O57" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O57" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P57" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q57" s="54">
         <v>44709</v>
@@ -6209,18 +6148,18 @@
         <v>0.68333333333333324</v>
       </c>
       <c r="S57" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T57" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U57" s="60"/>
       <c r="V57" s="61"/>
       <c r="W57" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>1</v>
       </c>
@@ -6237,37 +6176,37 @@
         <v>-116.978977</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J58" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>93</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M58" s="3">
         <v>12</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P58" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q58" s="54">
         <v>44713</v>
@@ -6276,18 +6215,18 @@
         <v>0.83124999999999993</v>
       </c>
       <c r="S58" s="59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T58" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U58" s="60"/>
       <c r="V58" s="61"/>
       <c r="W58" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
         <v>1</v>
       </c>
@@ -6304,35 +6243,35 @@
         <v>-118.153305</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H59" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I59" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J59" s="47"/>
       <c r="K59" s="3" t="s">
         <v>94</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M59" s="3">
         <v>4.16</v>
       </c>
       <c r="N59" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O59" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O59" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P59" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q59" s="54">
         <v>44714</v>
@@ -6341,18 +6280,18 @@
         <v>0.86458333333333337</v>
       </c>
       <c r="S59" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T59" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U59" s="60"/>
       <c r="V59" s="61"/>
       <c r="W59" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>1</v>
       </c>
@@ -6369,35 +6308,35 @@
         <v>-118.96733500000001</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="3" t="s">
         <v>95</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M60" s="3">
         <v>220</v>
       </c>
       <c r="N60" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O60" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O60" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P60" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q60" s="54"/>
       <c r="R60" s="55"/>
@@ -6406,16 +6345,16 @@
       </c>
       <c r="T60" s="60"/>
       <c r="U60" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V60" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W60" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W60" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="25" t="s">
         <v>1</v>
       </c>
@@ -6432,35 +6371,35 @@
         <v>-119.135215</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J61" s="47"/>
       <c r="K61" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M61" s="3">
         <v>12</v>
       </c>
       <c r="N61" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O61" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O61" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P61" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q61" s="54">
         <v>44717</v>
@@ -6469,18 +6408,18 @@
         <v>0.55347222222222225</v>
       </c>
       <c r="S61" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T61" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U61" s="60"/>
       <c r="V61" s="61"/>
       <c r="W61" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="25" t="s">
         <v>1</v>
       </c>
@@ -6497,37 +6436,37 @@
         <v>-117.41982899999999</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J62" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>96</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M62" s="3">
         <v>12</v>
       </c>
       <c r="N62" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O62" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O62" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P62" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q62" s="54">
         <v>44718</v>
@@ -6540,16 +6479,16 @@
       </c>
       <c r="T62" s="60"/>
       <c r="U62" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V62" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V62" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W62" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="25" t="s">
         <v>1</v>
       </c>
@@ -6566,35 +6505,35 @@
         <v>-118.069867</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I63" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J63" s="47"/>
       <c r="K63" s="3" t="s">
         <v>98</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M63" s="3">
         <v>12</v>
       </c>
       <c r="N63" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O63" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O63" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P63" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q63" s="54">
         <v>44719</v>
@@ -6607,16 +6546,16 @@
       </c>
       <c r="T63" s="60"/>
       <c r="U63" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V63" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W63" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W63" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="25" t="s">
         <v>1</v>
       </c>
@@ -6633,51 +6572,51 @@
         <v>-117.23595899999999</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H64" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J64" s="47"/>
       <c r="K64" s="3" t="s">
         <v>97</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M64" s="3">
         <v>12</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P64" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q64" s="54"/>
       <c r="R64" s="55"/>
       <c r="S64" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T64" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U64" s="60"/>
       <c r="V64" s="61"/>
       <c r="W64" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" s="25" t="s">
         <v>1</v>
       </c>
@@ -6694,35 +6633,35 @@
         <v>-118.12662400000001</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H65" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J65" s="49"/>
       <c r="K65" s="3" t="s">
         <v>99</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M65" s="3">
         <v>12</v>
       </c>
       <c r="N65" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O65" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P65" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="54">
         <v>44720</v>
@@ -6735,16 +6674,16 @@
       </c>
       <c r="T65" s="60"/>
       <c r="U65" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V65" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V65" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W65" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" s="25" t="s">
         <v>1</v>
       </c>
@@ -6761,62 +6700,62 @@
         <v>-118.151747</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J66" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>100</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M66" s="3">
         <v>16</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="P66" s="82" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q66" s="83">
+        <v>231</v>
+      </c>
+      <c r="P66" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q66" s="69">
         <v>44724</v>
       </c>
-      <c r="R66" s="84">
+      <c r="R66" s="70">
         <v>0.43333333333333335</v>
       </c>
       <c r="S66" s="59" t="s">
         <v>0</v>
       </c>
       <c r="T66" s="59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U66" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V66" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W66" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W66" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A67" s="93" t="s">
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B67" s="10">
@@ -6826,43 +6765,43 @@
         <v>0.375</v>
       </c>
       <c r="D67" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="E67" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="E67" s="23" t="s">
+      <c r="F67" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H67" s="74" t="s">
+        <v>167</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J67" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="K67" s="75" t="s">
         <v>263</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H67" s="88" t="s">
-        <v>168</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J67" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="K67" s="89" t="s">
-        <v>264</v>
-      </c>
       <c r="L67" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M67" s="3">
         <v>16</v>
       </c>
       <c r="N67" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O67" s="66" t="s">
         <v>231</v>
       </c>
-      <c r="O67" s="80" t="s">
-        <v>232</v>
-      </c>
       <c r="P67" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="54">
         <v>44725</v>
@@ -6870,20 +6809,19 @@
       <c r="R67" s="55">
         <v>0.36249999999999999</v>
       </c>
-      <c r="S67" s="81" t="s">
-        <v>250</v>
+      <c r="S67" s="67" t="s">
+        <v>249</v>
       </c>
       <c r="T67" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U67" s="60"/>
       <c r="V67" s="61"/>
       <c r="W67" s="59" t="s">
-        <v>169</v>
-      </c>
-      <c r="X67" s="92"/>
-    </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
         <v>1</v>
       </c>
@@ -6900,42 +6838,42 @@
         <v>36</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="I68" s="90" t="s">
-        <v>170</v>
-      </c>
-      <c r="J68" s="91" t="s">
-        <v>189</v>
+        <v>173</v>
+      </c>
+      <c r="I68" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="J68" s="77" t="s">
+        <v>188</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M68" s="3">
         <v>12</v>
       </c>
       <c r="N68" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O68" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O68" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="P68" s="85" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q68" s="86">
+      <c r="P68" s="71" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q68" s="72">
         <v>44728</v>
       </c>
-      <c r="R68" s="87">
+      <c r="R68" s="73">
         <v>0.52638888888888891</v>
       </c>
       <c r="S68" s="59" t="s">
@@ -6943,16 +6881,16 @@
       </c>
       <c r="T68" s="60"/>
       <c r="U68" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V68" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V68" s="61" t="s">
+      <c r="W68" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W68" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" s="25" t="s">
         <v>1</v>
       </c>
@@ -6969,37 +6907,37 @@
         <v>-119.519606</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J69" s="48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>101</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M69" s="3">
         <v>16</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P69" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="54">
         <v>44729</v>
@@ -7008,18 +6946,18 @@
         <v>0.81666666666666676</v>
       </c>
       <c r="S69" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T69" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U69" s="60"/>
       <c r="V69" s="61"/>
       <c r="W69" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
         <v>1</v>
       </c>
@@ -7036,35 +6974,35 @@
         <v>-118.60261800000001</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H70" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J70" s="47"/>
       <c r="K70" s="3" t="s">
         <v>102</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M70" s="3">
         <v>16</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P70" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="54">
         <v>44729</v>
@@ -7077,16 +7015,16 @@
       </c>
       <c r="T70" s="60"/>
       <c r="U70" s="59" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V70" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W70" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W70" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
         <v>1</v>
       </c>
@@ -7103,53 +7041,53 @@
         <v>-118.09059999999999</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J71" s="48" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>103</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M71" s="3">
         <v>500</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P71" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="57"/>
       <c r="R71" s="58"/>
       <c r="S71" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T71" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U71" s="60"/>
       <c r="V71" s="45"/>
       <c r="W71" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
         <v>1</v>
       </c>
@@ -7166,37 +7104,37 @@
         <v>-117.28451200000001</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H72" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J72" s="48" t="s">
         <v>168</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J72" s="48" t="s">
-        <v>169</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>104</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M72" s="3">
         <v>12</v>
       </c>
       <c r="N72" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O72" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O72" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P72" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="54">
         <v>44733</v>
@@ -7205,18 +7143,18 @@
         <v>0.6645833333333333</v>
       </c>
       <c r="S72" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U72" s="60"/>
       <c r="V72" s="61"/>
       <c r="W72" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
         <v>1</v>
       </c>
@@ -7233,35 +7171,35 @@
         <v>-116.674755</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H73" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J73" s="47"/>
       <c r="K73" s="3" t="s">
         <v>105</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M73" s="3">
         <v>12</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P73" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q73" s="54">
         <v>44734</v>
@@ -7270,18 +7208,18 @@
         <v>0.92291666666666661</v>
       </c>
       <c r="S73" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U73" s="60"/>
       <c r="V73" s="61"/>
       <c r="W73" s="61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
         <v>1</v>
       </c>
@@ -7298,53 +7236,53 @@
         <v>-118.556138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J74" s="48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>106</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M74" s="3">
         <v>16</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P74" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="54"/>
       <c r="R74" s="55"/>
       <c r="S74" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T74" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U74" s="60"/>
       <c r="V74" s="61"/>
       <c r="W74" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75" s="25" t="s">
         <v>1</v>
       </c>
@@ -7361,51 +7299,51 @@
         <v>-118.100279</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H75" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I75" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J75" s="51"/>
       <c r="K75" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M75" s="3">
         <v>66</v>
       </c>
       <c r="N75" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O75" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P75" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q75" s="51"/>
       <c r="R75" s="51"/>
       <c r="S75" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T75" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U75" s="60"/>
       <c r="V75" s="61"/>
       <c r="W75" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
         <v>1</v>
       </c>
@@ -7422,37 +7360,37 @@
         <v>-118.870828</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J76" s="48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>108</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M76" s="3">
         <v>16</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P76" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q76" s="54">
         <v>44736</v>
@@ -7461,18 +7399,18 @@
         <v>0.62986111111111109</v>
       </c>
       <c r="S76" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T76" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U76" s="60"/>
       <c r="V76" s="61"/>
       <c r="W76" s="61" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" s="25" t="s">
         <v>1</v>
       </c>
@@ -7489,37 +7427,37 @@
         <v>-118.69963300000001</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J77" s="48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>107</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M77" s="3">
         <v>66</v>
       </c>
       <c r="N77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O77" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O77" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P77" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q77" s="54"/>
       <c r="R77" s="55"/>
@@ -7528,16 +7466,16 @@
       </c>
       <c r="T77" s="60"/>
       <c r="U77" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V77" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W77" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W77" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" s="25" t="s">
         <v>1</v>
       </c>
@@ -7554,35 +7492,35 @@
         <v>-118.133798</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J78" s="49"/>
       <c r="K78" s="3" t="s">
         <v>109</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M78" s="3">
         <v>16</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P78" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="54">
         <v>44739</v>
@@ -7591,18 +7529,18 @@
         <v>0.64930555555555558</v>
       </c>
       <c r="S78" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T78" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U78" s="60"/>
       <c r="V78" s="61"/>
       <c r="W78" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" s="25" t="s">
         <v>1</v>
       </c>
@@ -7619,37 +7557,37 @@
         <v>-118.69743699999999</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J79" s="48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K79" s="3" t="s">
         <v>110</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M79" s="3">
         <v>16</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P79" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q79" s="54">
         <v>44740</v>
@@ -7658,18 +7596,18 @@
         <v>0.8027777777777777</v>
       </c>
       <c r="S79" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T79" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U79" s="60"/>
       <c r="V79" s="61"/>
       <c r="W79" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="25" t="s">
         <v>1</v>
       </c>
@@ -7686,37 +7624,37 @@
         <v>-117.914078</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J80" s="48" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>111</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M80" s="3">
         <v>12</v>
       </c>
       <c r="N80" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O80" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P80" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q80" s="54">
         <v>44746</v>
@@ -7729,16 +7667,16 @@
       </c>
       <c r="T80" s="60"/>
       <c r="U80" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V80" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V80" s="61" t="s">
+      <c r="W80" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W80" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" s="25" t="s">
         <v>1</v>
       </c>
@@ -7755,53 +7693,53 @@
         <v>-118.607972</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J81" s="48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>112</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M81" s="3">
         <v>220</v>
       </c>
       <c r="N81" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O81" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O81" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P81" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q81" s="54"/>
       <c r="R81" s="55"/>
       <c r="S81" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T81" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U81" s="60"/>
       <c r="V81" s="61"/>
       <c r="W81" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" s="25" t="s">
         <v>1</v>
       </c>
@@ -7818,35 +7756,35 @@
         <v>-117.93405</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H82" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I82" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J82" s="49"/>
       <c r="K82" s="3" t="s">
         <v>113</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M82" s="3">
         <v>12</v>
       </c>
       <c r="N82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O82" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O82" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P82" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q82" s="54">
         <v>44752</v>
@@ -7859,16 +7797,16 @@
       </c>
       <c r="T82" s="60"/>
       <c r="U82" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V82" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V82" s="61" t="s">
+      <c r="W82" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W82" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" s="25" t="s">
         <v>1</v>
       </c>
@@ -7885,35 +7823,35 @@
         <v>-118.829314</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H83" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I83" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J83" s="51"/>
       <c r="K83" s="3" t="s">
         <v>114</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M83" s="3">
         <v>16</v>
       </c>
       <c r="N83" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O83" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O83" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P83" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q83" s="54">
         <v>44752</v>
@@ -7926,16 +7864,16 @@
       </c>
       <c r="T83" s="51"/>
       <c r="U83" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V83" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W83" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W83" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="25" t="s">
         <v>1</v>
       </c>
@@ -7952,35 +7890,35 @@
         <v>-117.954875</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H84" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I84" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J84" s="47"/>
       <c r="K84" s="3" t="s">
         <v>115</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M84" s="3">
         <v>12</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P84" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q84" s="54"/>
       <c r="R84" s="55"/>
@@ -7989,16 +7927,16 @@
       </c>
       <c r="T84" s="60"/>
       <c r="U84" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V84" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W84" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W84" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" s="25" t="s">
         <v>1</v>
       </c>
@@ -8015,37 +7953,37 @@
         <v>-118.253387</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H85" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J85" s="48" t="s">
         <v>168</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J85" s="48" t="s">
-        <v>169</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M85" s="3">
         <v>16</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P85" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q85" s="54">
         <v>44756</v>
@@ -8054,18 +7992,18 @@
         <v>0.70347222222222217</v>
       </c>
       <c r="S85" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T85" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U85" s="60"/>
       <c r="V85" s="61"/>
       <c r="W85" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" s="25" t="s">
         <v>1</v>
       </c>
@@ -8082,35 +8020,35 @@
         <v>-117.927893</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H86" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I86" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J86" s="47"/>
       <c r="K86" s="3" t="s">
         <v>117</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M86" s="3">
         <v>12</v>
       </c>
       <c r="N86" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O86" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O86" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P86" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q86" s="54">
         <v>44758</v>
@@ -8119,22 +8057,22 @@
         <v>0.68055555555555547</v>
       </c>
       <c r="S86" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T86" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U86" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="V86" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="V86" s="61" t="s">
+      <c r="W86" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="W86" s="61" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" s="25" t="s">
         <v>1</v>
       </c>
@@ -8151,37 +8089,37 @@
         <v>-116.546813</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J87" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>118</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M87" s="3">
         <v>4.16</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P87" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q87" s="54">
         <v>44759</v>
@@ -8190,18 +8128,18 @@
         <v>0.91180555555555554</v>
       </c>
       <c r="S87" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T87" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U87" s="60"/>
       <c r="V87" s="61"/>
       <c r="W87" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" s="25" t="s">
         <v>1</v>
       </c>
@@ -8218,51 +8156,51 @@
         <v>-117.58870400000001</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H88" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J88" s="49"/>
       <c r="K88" s="3" t="s">
         <v>119</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M88" s="3">
         <v>12</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P88" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q88" s="54"/>
       <c r="R88" s="55"/>
       <c r="S88" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T88" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U88" s="60"/>
       <c r="V88" s="61"/>
       <c r="W88" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
         <v>1</v>
       </c>
@@ -8279,35 +8217,35 @@
         <v>-118.20227</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H89" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I89" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J89" s="49"/>
       <c r="K89" s="3" t="s">
         <v>120</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M89" s="3">
         <v>12</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P89" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q89" s="54">
         <v>44768</v>
@@ -8316,18 +8254,18 @@
         <v>0.24861111111111112</v>
       </c>
       <c r="S89" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T89" s="59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U89" s="60"/>
       <c r="V89" s="61"/>
       <c r="W89" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" s="25" t="s">
         <v>1</v>
       </c>
@@ -8344,51 +8282,51 @@
         <v>-119.232202</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H90" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J90" s="51"/>
       <c r="K90" s="3" t="s">
         <v>122</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M90" s="3">
         <v>16</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P90" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q90" s="54"/>
       <c r="R90" s="55"/>
       <c r="S90" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T90" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U90" s="60"/>
       <c r="V90" s="61"/>
       <c r="W90" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>1</v>
       </c>
@@ -8405,35 +8343,35 @@
         <v>-117.192261</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H91" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J91" s="51"/>
       <c r="K91" s="3" t="s">
         <v>121</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M91" s="3">
         <v>12</v>
       </c>
       <c r="N91" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O91" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P91" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q91" s="54">
         <v>44771</v>
@@ -8445,19 +8383,19 @@
         <v>0</v>
       </c>
       <c r="T91" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U91" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V91" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V91" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W91" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>1</v>
       </c>
@@ -8474,51 +8412,51 @@
         <v>-118.71295499999999</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H92" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I92" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J92" s="49"/>
       <c r="K92" s="3" t="s">
         <v>123</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M92" s="3">
         <v>16</v>
       </c>
       <c r="N92" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O92" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P92" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q92" s="54"/>
       <c r="R92" s="55"/>
       <c r="S92" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T92" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U92" s="60"/>
       <c r="V92" s="61"/>
       <c r="W92" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>1</v>
       </c>
@@ -8535,37 +8473,37 @@
         <v>-119.005807</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J93" s="48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>124</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M93" s="3">
         <v>16</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P93" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q93" s="54">
         <v>44782</v>
@@ -8574,18 +8512,18 @@
         <v>0.74930555555555556</v>
       </c>
       <c r="S93" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T93" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U93" s="60"/>
       <c r="V93" s="61"/>
       <c r="W93" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>1</v>
       </c>
@@ -8602,37 +8540,37 @@
         <v>-117.90338800000001</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J94" s="48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>125</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M94" s="3">
         <v>12</v>
       </c>
       <c r="N94" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O94" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P94" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q94" s="54"/>
       <c r="R94" s="55"/>
@@ -8640,19 +8578,19 @@
         <v>0</v>
       </c>
       <c r="T94" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U94" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V94" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W94" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W94" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>1</v>
       </c>
@@ -8669,53 +8607,53 @@
         <v>-117.31474</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J95" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>126</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M95" s="3">
         <v>12</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P95" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q95" s="54"/>
       <c r="R95" s="55"/>
       <c r="S95" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T95" s="59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="U95" s="60"/>
       <c r="V95" s="61"/>
       <c r="W95" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>1</v>
       </c>
@@ -8732,37 +8670,37 @@
         <v>-117.879627</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J96" s="48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>127</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M96" s="3">
         <v>12</v>
       </c>
       <c r="N96" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O96" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O96" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P96" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q96" s="54">
         <v>44784</v>
@@ -8774,19 +8712,19 @@
         <v>0</v>
       </c>
       <c r="T96" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U96" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V96" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W96" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W96" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>1</v>
       </c>
@@ -8803,35 +8741,35 @@
         <v>-117.38855700000001</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H97" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J97" s="47"/>
       <c r="K97" s="3" t="s">
         <v>128</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M97" s="3">
         <v>12</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P97" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q97" s="54">
         <v>44787</v>
@@ -8840,18 +8778,18 @@
         <v>0.12569444444444444</v>
       </c>
       <c r="S97" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T97" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U97" s="60"/>
       <c r="V97" s="61"/>
       <c r="W97" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>1</v>
       </c>
@@ -8868,37 +8806,37 @@
         <v>-119.244508</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J98" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>129</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M98" s="3">
         <v>12</v>
       </c>
       <c r="N98" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O98" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O98" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P98" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q98" s="54">
         <v>44791</v>
@@ -8910,19 +8848,19 @@
         <v>0</v>
       </c>
       <c r="T98" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U98" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V98" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V98" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W98" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>1</v>
       </c>
@@ -8939,35 +8877,35 @@
         <v>-118.423067</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J99" s="49"/>
       <c r="K99" s="3" t="s">
         <v>130</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M99" s="3">
         <v>66</v>
       </c>
       <c r="N99" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O99" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O99" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P99" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q99" s="54"/>
       <c r="R99" s="55"/>
@@ -8975,19 +8913,19 @@
         <v>0</v>
       </c>
       <c r="T99" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U99" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V99" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="V99" s="61" t="s">
-        <v>249</v>
-      </c>
       <c r="W99" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>1</v>
       </c>
@@ -9004,51 +8942,51 @@
         <v>-118.37387</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H100" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I100" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J100" s="47"/>
       <c r="K100" s="3" t="s">
         <v>131</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M100" s="3">
         <v>16</v>
       </c>
       <c r="N100" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O100" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O100" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P100" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q100" s="54"/>
       <c r="R100" s="55"/>
       <c r="S100" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T100" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U100" s="60"/>
       <c r="V100" s="61"/>
       <c r="W100" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>1</v>
       </c>
@@ -9065,35 +9003,35 @@
         <v>-119.18571369999999</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J101" s="47"/>
       <c r="K101" s="3" t="s">
         <v>132</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M101" s="3">
         <v>66</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P101" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q101" s="54"/>
       <c r="R101" s="55"/>
@@ -9101,19 +9039,19 @@
         <v>0</v>
       </c>
       <c r="T101" s="59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U101" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V101" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W101" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W101" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>1</v>
       </c>
@@ -9130,37 +9068,37 @@
         <v>-119.411129</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J102" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>133</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M102" s="3">
         <v>12</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P102" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q102" s="54">
         <v>44801</v>
@@ -9169,18 +9107,18 @@
         <v>0.78402777777777777</v>
       </c>
       <c r="S102" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T102" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U102" s="60"/>
       <c r="V102" s="60"/>
       <c r="W102" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>1</v>
       </c>
@@ -9197,35 +9135,35 @@
         <v>-118.103835</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H103" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I103" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I103" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J103" s="47"/>
       <c r="K103" s="3" t="s">
         <v>134</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M103" s="3">
         <v>16</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P103" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q103" s="54">
         <v>44804</v>
@@ -9234,18 +9172,18 @@
         <v>0.56041666666666667</v>
       </c>
       <c r="S103" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T103" s="59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="U103" s="60"/>
       <c r="V103" s="60"/>
       <c r="W103" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>1</v>
       </c>
@@ -9262,37 +9200,37 @@
         <v>38</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J104" s="48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>135</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M104" s="3">
         <v>16</v>
       </c>
       <c r="N104" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O104" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O104" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P104" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q104" s="54">
         <v>44805</v>
@@ -9301,18 +9239,18 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="S104" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T104" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U104" s="60"/>
       <c r="V104" s="60"/>
       <c r="W104" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>1</v>
       </c>
@@ -9329,37 +9267,37 @@
         <v>-118.012435</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J105" s="48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>136</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M105" s="3">
         <v>12</v>
       </c>
       <c r="N105" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O105" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O105" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P105" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q105" s="54">
         <v>44807</v>
@@ -9371,19 +9309,19 @@
         <v>0</v>
       </c>
       <c r="T105" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U105" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="V105" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="V105" s="59" t="s">
-        <v>249</v>
-      </c>
       <c r="W105" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>1</v>
       </c>
@@ -9400,53 +9338,53 @@
         <v>-118.84327999999999</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J106" s="48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>137</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M106" s="3">
         <v>16</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P106" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q106" s="54"/>
       <c r="R106" s="55"/>
       <c r="S106" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T106" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U106" s="60"/>
       <c r="V106" s="60"/>
       <c r="W106" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>1</v>
       </c>
@@ -9463,51 +9401,51 @@
         <v>-117.617733</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H107" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I107" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J107" s="47"/>
       <c r="K107" s="3" t="s">
         <v>138</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M107" s="3">
         <v>12</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P107" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q107" s="54"/>
       <c r="R107" s="55"/>
       <c r="S107" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T107" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U107" s="60"/>
       <c r="V107" s="60"/>
       <c r="W107" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>1</v>
       </c>
@@ -9524,35 +9462,35 @@
         <v>40</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H108" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I108" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="4" t="s">
         <v>139</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M108" s="3">
         <v>12</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P108" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q108" s="54">
         <v>44810</v>
@@ -9561,18 +9499,18 @@
         <v>0.4826388888888889</v>
       </c>
       <c r="S108" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T108" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U108" s="60"/>
       <c r="V108" s="60"/>
       <c r="W108" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>1</v>
       </c>
@@ -9589,35 +9527,35 @@
         <v>-118.76801399999999</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J109" s="49"/>
       <c r="K109" s="3" t="s">
         <v>140</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M109" s="3">
         <v>12</v>
       </c>
       <c r="N109" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O109" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O109" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P109" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q109" s="54">
         <v>44810</v>
@@ -9626,20 +9564,20 @@
         <v>0.80763888888888891</v>
       </c>
       <c r="S109" s="64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T109" s="60"/>
       <c r="U109" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="V109" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W109" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>1</v>
       </c>
@@ -9656,37 +9594,37 @@
         <v>-119.03934099999999</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J110" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>141</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M110" s="3">
         <v>220</v>
       </c>
       <c r="N110" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O110" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O110" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P110" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q110" s="54"/>
       <c r="R110" s="55"/>
@@ -9694,19 +9632,19 @@
         <v>0</v>
       </c>
       <c r="T110" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U110" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V110" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="W110" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W110" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>1</v>
       </c>
@@ -9723,35 +9661,35 @@
         <v>-118.638372</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J111" s="52"/>
       <c r="K111" s="3" t="s">
         <v>142</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M111" s="3">
         <v>2.4</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P111" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q111" s="54">
         <v>44813</v>
@@ -9760,18 +9698,18 @@
         <v>0.7402777777777777</v>
       </c>
       <c r="S111" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T111" s="59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U111" s="65"/>
       <c r="V111" s="65"/>
       <c r="W111" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>1</v>
       </c>
@@ -9788,37 +9726,37 @@
         <v>-117.38909</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J112" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>143</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M112" s="3">
         <v>12</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P112" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q112" s="54">
         <v>44831</v>
@@ -9827,18 +9765,18 @@
         <v>0.57708333333333328</v>
       </c>
       <c r="S112" s="59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T112" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U112" s="65"/>
       <c r="V112" s="65"/>
       <c r="W112" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>1</v>
       </c>
@@ -9855,37 +9793,37 @@
         <v>-119.23418599999999</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J113" s="50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>144</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M113" s="3">
         <v>16</v>
       </c>
       <c r="N113" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O113" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P113" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q113" s="54">
         <v>44832</v>
@@ -9897,19 +9835,19 @@
         <v>0</v>
       </c>
       <c r="T113" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U113" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V113" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W113" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W113" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>1</v>
       </c>
@@ -9926,35 +9864,35 @@
         <v>-119.036068</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J114" s="52"/>
       <c r="K114" s="3" t="s">
         <v>145</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M114" s="3">
         <v>220</v>
       </c>
       <c r="N114" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O114" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O114" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P114" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q114" s="54"/>
       <c r="R114" s="55"/>
@@ -9962,19 +9900,19 @@
         <v>0</v>
       </c>
       <c r="T114" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U114" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V114" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W114" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W114" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>1</v>
       </c>
@@ -9991,37 +9929,37 @@
         <v>42</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J115" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>146</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M115" s="3">
         <v>16</v>
       </c>
       <c r="N115" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O115" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O115" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P115" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q115" s="54">
         <v>44836</v>
@@ -10030,18 +9968,18 @@
         <v>0.67291666666666661</v>
       </c>
       <c r="S115" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T115" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U115" s="60"/>
       <c r="V115" s="60"/>
       <c r="W115" s="59" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>1</v>
       </c>
@@ -10058,35 +9996,35 @@
         <v>-118.120288</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H116" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I116" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J116" s="49"/>
       <c r="K116" s="3" t="s">
         <v>147</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M116" s="3">
         <v>12</v>
       </c>
       <c r="N116" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O116" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O116" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P116" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q116" s="54">
         <v>44843</v>
@@ -10098,19 +10036,19 @@
         <v>0</v>
       </c>
       <c r="T116" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U116" s="59" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V116" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W116" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W116" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>1</v>
       </c>
@@ -10127,35 +10065,35 @@
         <v>-117.268523</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J117" s="49"/>
       <c r="K117" s="3" t="s">
         <v>148</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M117" s="3">
         <v>12</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O117" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P117" s="56" t="s">
         <v>239</v>
-      </c>
-      <c r="P117" s="56" t="s">
-        <v>240</v>
       </c>
       <c r="Q117" s="54">
         <v>44844</v>
@@ -10164,18 +10102,18 @@
         <v>0.83750000000000002</v>
       </c>
       <c r="S117" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T117" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U117" s="60"/>
       <c r="V117" s="60"/>
       <c r="W117" s="59" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>1</v>
       </c>
@@ -10192,51 +10130,51 @@
         <v>-119.385018</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J118" s="49"/>
       <c r="K118" s="4" t="s">
         <v>149</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M118" s="3">
         <v>16</v>
       </c>
       <c r="N118" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O118" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P118" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q118" s="54"/>
       <c r="R118" s="55"/>
       <c r="S118" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T118" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U118" s="60"/>
       <c r="V118" s="60"/>
       <c r="W118" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>1</v>
       </c>
@@ -10253,35 +10191,35 @@
         <v>-114.720563</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H119" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I119" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J119" s="49"/>
       <c r="K119" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M119" s="3">
         <v>12</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P119" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q119" s="54">
         <v>44864</v>
@@ -10290,18 +10228,18 @@
         <v>0.15</v>
       </c>
       <c r="S119" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T119" s="59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="U119" s="60"/>
       <c r="V119" s="60"/>
       <c r="W119" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
         <v>1</v>
       </c>
@@ -10318,53 +10256,53 @@
         <v>-119.065185</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J120" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>150</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M120" s="3">
         <v>16</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P120" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q120" s="54"/>
       <c r="R120" s="55"/>
       <c r="S120" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T120" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U120" s="60"/>
       <c r="V120" s="60"/>
       <c r="W120" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>1</v>
       </c>
@@ -10381,51 +10319,51 @@
         <v>-118.010409</v>
       </c>
       <c r="F121" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G121" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G121" s="18" t="s">
-        <v>163</v>
-      </c>
       <c r="H121" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I121" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I121" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="3" t="s">
         <v>151</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M121" s="3">
         <v>12</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P121" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q121" s="54"/>
       <c r="R121" s="55"/>
       <c r="S121" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T121" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U121" s="60"/>
       <c r="V121" s="60"/>
       <c r="W121" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>1</v>
       </c>
@@ -10442,35 +10380,35 @@
         <v>-117.88027099999999</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H122" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I122" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I122" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="4" t="s">
         <v>152</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M122" s="3">
         <v>12</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O122" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P122" s="56" t="s">
         <v>239</v>
-      </c>
-      <c r="P122" s="56" t="s">
-        <v>240</v>
       </c>
       <c r="Q122" s="54">
         <v>44869</v>
@@ -10479,18 +10417,18 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="S122" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T122" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U122" s="60"/>
       <c r="V122" s="60"/>
       <c r="W122" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>1</v>
       </c>
@@ -10507,37 +10445,37 @@
         <v>-118.59916200000001</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J123" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K123" s="3" t="s">
         <v>153</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M123" s="3">
         <v>16</v>
       </c>
       <c r="N123" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O123" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O123" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P123" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q123" s="54">
         <v>44881</v>
@@ -10549,19 +10487,19 @@
         <v>0</v>
       </c>
       <c r="T123" s="59" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U123" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V123" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W123" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>1</v>
       </c>
@@ -10578,35 +10516,35 @@
         <v>-118.12688300000001</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H124" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I124" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J124" s="49"/>
       <c r="K124" s="3" t="s">
         <v>154</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M124" s="3">
         <v>16</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P124" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q124" s="54">
         <v>44886</v>
@@ -10615,18 +10553,18 @@
         <v>0.93958333333333333</v>
       </c>
       <c r="S124" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T124" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U124" s="60"/>
       <c r="V124" s="60"/>
       <c r="W124" s="59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>1</v>
       </c>
@@ -10643,37 +10581,37 @@
         <v>-117.433295</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J125" s="50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>155</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M125" s="3">
         <v>12</v>
       </c>
       <c r="N125" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O125" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O125" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P125" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q125" s="54">
         <v>44888</v>
@@ -10685,19 +10623,19 @@
         <v>0</v>
       </c>
       <c r="T125" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U125" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V125" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W125" s="59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>1</v>
       </c>
@@ -10714,37 +10652,37 @@
         <v>-117.824574</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J126" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>156</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M126" s="3">
         <v>12</v>
       </c>
       <c r="N126" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O126" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="O126" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="P126" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q126" s="54">
         <v>44892</v>
@@ -10757,16 +10695,16 @@
       </c>
       <c r="T126" s="60"/>
       <c r="U126" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V126" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W126" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="W126" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>1</v>
       </c>
@@ -10783,53 +10721,53 @@
         <v>-117.703222</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J127" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>157</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M127" s="3">
         <v>12</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P127" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q127" s="54"/>
       <c r="R127" s="55"/>
       <c r="S127" s="59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T127" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U127" s="60"/>
       <c r="V127" s="60"/>
       <c r="W127" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>1</v>
       </c>
@@ -10846,35 +10784,35 @@
         <v>-117.17903200000001</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H128" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I128" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I128" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J128" s="49"/>
       <c r="K128" s="3" t="s">
         <v>158</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M128" s="3">
         <v>12</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O128" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P128" s="56" t="s">
         <v>239</v>
-      </c>
-      <c r="P128" s="56" t="s">
-        <v>240</v>
       </c>
       <c r="Q128" s="54">
         <v>44921</v>
@@ -10886,16 +10824,16 @@
         <v>0</v>
       </c>
       <c r="T128" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U128" s="59" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V128" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="W128" s="59" t="s">
         <v>243</v>
-      </c>
-      <c r="W128" s="59" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -10909,64 +10847,24 @@
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q39:Q55 Q26:Q36 Q57:Q69 Q72:Q128">
-    <cfRule type="expression" dxfId="11" priority="12">
-      <formula>IF(P26="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R39:R55 R26:R36 R57:R69 R72:R128">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>IF(P26="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q7 Q9:Q22">
-    <cfRule type="expression" dxfId="9" priority="10">
+  <conditionalFormatting sqref="Q3:Q69">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>IF(P3="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R7 R9:R22">
-    <cfRule type="expression" dxfId="8" priority="9">
+  <conditionalFormatting sqref="Q72:Q128">
+    <cfRule type="expression" dxfId="2" priority="12">
+      <formula>IF(P72="No",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R69">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>IF(P3="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q8">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>IF(P8="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R8">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>IF(P8="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q23:Q25">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>IF(P23="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R23:R25">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>IF(P23="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q37:Q38">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>IF(P37="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R37:R38">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>IF(P37="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q56">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>IF(P56="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R56">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IF(P56="No",TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="R72:R128">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>IF(P72="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11227,9 +11125,29 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7F4A51-C189-47DA-9971-00FBB8065764}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7F4A51-C189-47DA-9971-00FBB8065764}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3959da87-2c1f-450f-8c1c-0f8601c1696c"/>
+    <ds:schemaRef ds:uri="e5e7f03b-50cd-4083-b406-aada361f4e1d"/>
+    <ds:schemaRef ds:uri="e45da448-bf9c-43e8-8676-7e88d583ded9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BFDBB32-F6C4-4DF7-AE17-B0ECE5A0EEA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BFDBB32-F6C4-4DF7-AE17-B0ECE5A0EEA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>